--- a/Figures_code.xlsx
+++ b/Figures_code.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anna\Dropbox\Agrp\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8367361E-DCCC-40B6-A327-9A4705873D8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA58ECB-7A34-4363-A7C1-8455CDBA7271}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5268" xr2:uid="{8B34050A-13E4-4577-9C0B-094835B9E9BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="96">
   <si>
     <t>Figure (plot)</t>
   </si>
@@ -117,15 +117,6 @@
     <t>S1B,D</t>
   </si>
   <si>
-    <t>S2A-F</t>
-  </si>
-  <si>
-    <t>S2G</t>
-  </si>
-  <si>
-    <t>S2H</t>
-  </si>
-  <si>
     <t>S4B,C,E,F</t>
   </si>
   <si>
@@ -133,12 +124,6 @@
   </si>
   <si>
     <t>one_source_maze_pipeline</t>
-  </si>
-  <si>
-    <t>S1E,F</t>
-  </si>
-  <si>
-    <t>S1G,H</t>
   </si>
   <si>
     <t>Raster plot food discovery</t>
@@ -288,6 +273,57 @@
   </si>
   <si>
     <t>1L,M</t>
+  </si>
+  <si>
+    <t>2K,M</t>
+  </si>
+  <si>
+    <t>Runs after food visit vs after eating</t>
+  </si>
+  <si>
+    <t>2L,N</t>
+  </si>
+  <si>
+    <t>Slopes (for the behavior - visit vs eating)</t>
+  </si>
+  <si>
+    <t>Averaged both types of runs dynamic</t>
+  </si>
+  <si>
+    <t>2O_R</t>
+  </si>
+  <si>
+    <t>S1E-H</t>
+  </si>
+  <si>
+    <t>S1I-L</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>one_source_thirst</t>
+  </si>
+  <si>
+    <t>S3I</t>
+  </si>
+  <si>
+    <t>S3J</t>
+  </si>
+  <si>
+    <t>S3K</t>
+  </si>
+  <si>
+    <t>Raster plot water discovery</t>
+  </si>
+  <si>
+    <t>Compare correlations before and after water discovery</t>
+  </si>
+  <si>
+    <t>S4O,P</t>
+  </si>
+  <si>
+    <t>Compare conditions speed and traveled distance</t>
   </si>
 </sst>
 </file>
@@ -666,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3096603B-9AA9-44BD-8B75-912348CABA7D}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
@@ -702,63 +738,63 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -766,13 +802,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -780,13 +816,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -794,418 +830,479 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>68</v>
       </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" t="s">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" t="s">
         <v>35</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
